--- a/artfynd/A 57103-2024 artfynd.xlsx
+++ b/artfynd/A 57103-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122309878</v>
+        <v>122310991</v>
       </c>
       <c r="B2" t="n">
         <v>78645</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>442738</v>
+        <v>442697</v>
       </c>
       <c r="R2" t="n">
-        <v>7038100</v>
+        <v>7038320</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122309300</v>
+        <v>122307791</v>
       </c>
       <c r="B3" t="n">
         <v>78645</v>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>442336</v>
+        <v>442231</v>
       </c>
       <c r="R3" t="n">
-        <v>7038072</v>
+        <v>7037925</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,11 +878,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-01-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +929,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122310558</v>
+        <v>122311105</v>
       </c>
       <c r="B4" t="n">
         <v>78645</v>
@@ -974,10 +969,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>442820</v>
+        <v>442624</v>
       </c>
       <c r="R4" t="n">
-        <v>7038222</v>
+        <v>7038299</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1061,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122307645</v>
+        <v>122308101</v>
       </c>
       <c r="B5" t="n">
-        <v>78645</v>
+        <v>74739</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,34 +1072,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Pålflon, Pålflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>442212</v>
+        <v>442234</v>
       </c>
       <c r="R5" t="n">
-        <v>7037987</v>
+        <v>7037901</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1155,22 +1155,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Betula</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122310094</v>
+        <v>122310558</v>
       </c>
       <c r="B6" t="n">
         <v>78645</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442814</v>
+        <v>442820</v>
       </c>
       <c r="R6" t="n">
-        <v>7038112</v>
+        <v>7038222</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1315,10 +1315,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122310208</v>
+        <v>122309178</v>
       </c>
       <c r="B7" t="n">
-        <v>90797</v>
+        <v>78645</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1331,48 +1331,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Pålflon, Pålflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442811</v>
+        <v>442255</v>
       </c>
       <c r="R7" t="n">
-        <v>7038110</v>
+        <v>7037977</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1433,12 +1419,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1456,7 +1442,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122309386</v>
+        <v>122311042</v>
       </c>
       <c r="B8" t="n">
         <v>78645</v>
@@ -1496,10 +1482,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>442363</v>
+        <v>442677</v>
       </c>
       <c r="R8" t="n">
-        <v>7038109</v>
+        <v>7038353</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1532,11 +1518,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På en hyfsat grov gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1588,7 +1569,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122307791</v>
+        <v>122310094</v>
       </c>
       <c r="B9" t="n">
         <v>78645</v>
@@ -1628,10 +1609,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>442231</v>
+        <v>442814</v>
       </c>
       <c r="R9" t="n">
-        <v>7037925</v>
+        <v>7038112</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1715,7 +1696,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122311105</v>
+        <v>122309878</v>
       </c>
       <c r="B10" t="n">
         <v>78645</v>
@@ -1755,10 +1736,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>442624</v>
+        <v>442738</v>
       </c>
       <c r="R10" t="n">
-        <v>7038299</v>
+        <v>7038100</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1842,10 +1823,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122311042</v>
+        <v>122310586</v>
       </c>
       <c r="B11" t="n">
-        <v>78645</v>
+        <v>90797</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1858,34 +1839,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Pålflon, Pålflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>442677</v>
+        <v>442827</v>
       </c>
       <c r="R11" t="n">
-        <v>7038353</v>
+        <v>7038252</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1946,12 +1941,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1969,10 +1964,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122308101</v>
+        <v>122307542</v>
       </c>
       <c r="B12" t="n">
-        <v>74739</v>
+        <v>78645</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1985,39 +1980,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Pålflon, Pålflon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>442234</v>
+        <v>442196</v>
       </c>
       <c r="R12" t="n">
-        <v>7037901</v>
+        <v>7037947</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2068,22 +2058,22 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2101,7 +2091,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122310991</v>
+        <v>122309695</v>
       </c>
       <c r="B13" t="n">
         <v>78645</v>
@@ -2141,10 +2131,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>442697</v>
+        <v>442620</v>
       </c>
       <c r="R13" t="n">
-        <v>7038320</v>
+        <v>7038131</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2228,7 +2218,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122310586</v>
+        <v>122310208</v>
       </c>
       <c r="B14" t="n">
         <v>90797</v>
@@ -2263,7 +2253,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2282,10 +2272,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>442827</v>
+        <v>442811</v>
       </c>
       <c r="R14" t="n">
-        <v>7038252</v>
+        <v>7038110</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2369,10 +2359,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122308964</v>
+        <v>122309386</v>
       </c>
       <c r="B15" t="n">
-        <v>57527</v>
+        <v>78645</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2385,48 +2375,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Pålflon, Pålflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>442289</v>
+        <v>442363</v>
       </c>
       <c r="R15" t="n">
-        <v>7037939</v>
+        <v>7038109</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2461,6 +2437,11 @@
           <t>2025-01-25</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På en hyfsat grov gran.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2473,6 +2454,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2490,7 +2491,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122309695</v>
+        <v>122307645</v>
       </c>
       <c r="B16" t="n">
         <v>78645</v>
@@ -2530,10 +2531,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>442620</v>
+        <v>442212</v>
       </c>
       <c r="R16" t="n">
-        <v>7038131</v>
+        <v>7037987</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2617,7 +2618,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122307542</v>
+        <v>122309300</v>
       </c>
       <c r="B17" t="n">
         <v>78645</v>
@@ -2657,10 +2658,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>442196</v>
+        <v>442336</v>
       </c>
       <c r="R17" t="n">
-        <v>7037947</v>
+        <v>7038072</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2693,6 +2694,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2744,10 +2750,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122309178</v>
+        <v>122308964</v>
       </c>
       <c r="B18" t="n">
-        <v>78645</v>
+        <v>57527</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2760,34 +2766,48 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Pålflon, Pålflon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>442255</v>
+        <v>442289</v>
       </c>
       <c r="R18" t="n">
-        <v>7037977</v>
+        <v>7037939</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2834,26 +2854,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2871,10 +2871,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122349585</v>
+        <v>122349598</v>
       </c>
       <c r="B19" t="n">
-        <v>90744</v>
+        <v>78645</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2883,25 +2883,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>442240</v>
+        <v>442373</v>
       </c>
       <c r="R19" t="n">
-        <v>7037890</v>
+        <v>7038074</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2973,10 +2973,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122349605</v>
+        <v>122349586</v>
       </c>
       <c r="B20" t="n">
-        <v>82432</v>
+        <v>90779</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2989,21 +2989,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3013,10 +3013,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>442220</v>
+        <v>442757</v>
       </c>
       <c r="R20" t="n">
-        <v>7037923</v>
+        <v>7038151</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3075,7 +3075,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122349594</v>
+        <v>122349601</v>
       </c>
       <c r="B21" t="n">
         <v>78645</v>
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>442887</v>
+        <v>442336</v>
       </c>
       <c r="R21" t="n">
-        <v>7038257</v>
+        <v>7037800</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3177,10 +3177,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122349582</v>
+        <v>122349594</v>
       </c>
       <c r="B22" t="n">
-        <v>90744</v>
+        <v>78645</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3189,25 +3189,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>442586</v>
+        <v>442887</v>
       </c>
       <c r="R22" t="n">
-        <v>7038093</v>
+        <v>7038257</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3279,10 +3279,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122349589</v>
+        <v>122349595</v>
       </c>
       <c r="B23" t="n">
-        <v>90797</v>
+        <v>78645</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3295,21 +3295,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3319,10 +3319,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>442587</v>
+        <v>442823</v>
       </c>
       <c r="R23" t="n">
-        <v>7038092</v>
+        <v>7038118</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3381,7 +3381,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122349597</v>
+        <v>122349593</v>
       </c>
       <c r="B24" t="n">
         <v>78645</v>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>442485</v>
+        <v>442730</v>
       </c>
       <c r="R24" t="n">
-        <v>7038061</v>
+        <v>7038283</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3483,10 +3483,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122349599</v>
+        <v>122349582</v>
       </c>
       <c r="B25" t="n">
-        <v>78645</v>
+        <v>90744</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3495,25 +3495,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3523,10 +3523,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>442284</v>
+        <v>442586</v>
       </c>
       <c r="R25" t="n">
-        <v>7037922</v>
+        <v>7038093</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3585,7 +3585,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122349588</v>
+        <v>122349589</v>
       </c>
       <c r="B26" t="n">
         <v>90797</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>442307</v>
+        <v>442587</v>
       </c>
       <c r="R26" t="n">
-        <v>7038077</v>
+        <v>7038092</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3687,10 +3687,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122349586</v>
+        <v>122349592</v>
       </c>
       <c r="B27" t="n">
-        <v>90779</v>
+        <v>78645</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3703,21 +3703,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>442757</v>
+        <v>442680</v>
       </c>
       <c r="R27" t="n">
-        <v>7038151</v>
+        <v>7038286</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3789,10 +3789,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122349578</v>
+        <v>122349585</v>
       </c>
       <c r="B28" t="n">
-        <v>74747</v>
+        <v>90744</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3801,25 +3801,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>442199</v>
+        <v>442240</v>
       </c>
       <c r="R28" t="n">
-        <v>7037955</v>
+        <v>7037890</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122349584</v>
+        <v>122349605</v>
       </c>
       <c r="B29" t="n">
-        <v>90744</v>
+        <v>82432</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3903,25 +3903,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3931,10 +3931,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>442585</v>
+        <v>442220</v>
       </c>
       <c r="R29" t="n">
-        <v>7038064</v>
+        <v>7037923</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3993,10 +3993,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122349602</v>
+        <v>122349587</v>
       </c>
       <c r="B30" t="n">
-        <v>78645</v>
+        <v>90797</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4009,21 +4009,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4033,10 +4033,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>442214</v>
+        <v>442707</v>
       </c>
       <c r="R30" t="n">
-        <v>7037932</v>
+        <v>7038163</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4095,7 +4095,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122349587</v>
+        <v>122349588</v>
       </c>
       <c r="B31" t="n">
         <v>90797</v>
@@ -4135,10 +4135,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>442707</v>
+        <v>442307</v>
       </c>
       <c r="R31" t="n">
-        <v>7038163</v>
+        <v>7038077</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4197,10 +4197,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122349593</v>
+        <v>122349590</v>
       </c>
       <c r="B32" t="n">
-        <v>78645</v>
+        <v>90797</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4213,21 +4213,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4237,10 +4237,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>442730</v>
+        <v>442165</v>
       </c>
       <c r="R32" t="n">
-        <v>7038283</v>
+        <v>7037916</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4299,10 +4299,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122349590</v>
+        <v>122349584</v>
       </c>
       <c r="B33" t="n">
-        <v>90797</v>
+        <v>90744</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4311,25 +4311,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4339,10 +4339,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>442165</v>
+        <v>442585</v>
       </c>
       <c r="R33" t="n">
-        <v>7037916</v>
+        <v>7038064</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4401,7 +4401,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122349595</v>
+        <v>122349597</v>
       </c>
       <c r="B34" t="n">
         <v>78645</v>
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>442823</v>
+        <v>442485</v>
       </c>
       <c r="R34" t="n">
-        <v>7038118</v>
+        <v>7038061</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4707,10 +4707,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122349598</v>
+        <v>122349578</v>
       </c>
       <c r="B37" t="n">
-        <v>78645</v>
+        <v>74747</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4723,21 +4723,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4747,10 +4747,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>442373</v>
+        <v>442199</v>
       </c>
       <c r="R37" t="n">
-        <v>7038074</v>
+        <v>7037955</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4809,7 +4809,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122349592</v>
+        <v>122349599</v>
       </c>
       <c r="B38" t="n">
         <v>78645</v>
@@ -4849,10 +4849,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>442680</v>
+        <v>442284</v>
       </c>
       <c r="R38" t="n">
-        <v>7038286</v>
+        <v>7037922</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4911,7 +4911,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122349601</v>
+        <v>122349602</v>
       </c>
       <c r="B39" t="n">
         <v>78645</v>
@@ -4951,10 +4951,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>442336</v>
+        <v>442214</v>
       </c>
       <c r="R39" t="n">
-        <v>7037800</v>
+        <v>7037932</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5013,10 +5013,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122360805</v>
+        <v>122360814</v>
       </c>
       <c r="B40" t="n">
-        <v>57390</v>
+        <v>90797</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5029,21 +5029,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>442717</v>
+        <v>442329</v>
       </c>
       <c r="R40" t="n">
-        <v>7038375</v>
+        <v>7037884</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5089,11 +5089,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-01-25</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>färska hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5120,10 +5115,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122360810</v>
+        <v>122360803</v>
       </c>
       <c r="B41" t="n">
-        <v>90797</v>
+        <v>57374</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5136,21 +5131,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5160,10 +5155,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>442871</v>
+        <v>442741</v>
       </c>
       <c r="R41" t="n">
-        <v>7038224</v>
+        <v>7038374</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5196,6 +5191,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5222,10 +5222,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122360814</v>
+        <v>122360805</v>
       </c>
       <c r="B42" t="n">
-        <v>90797</v>
+        <v>57390</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5238,21 +5238,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5262,10 +5262,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>442329</v>
+        <v>442717</v>
       </c>
       <c r="R42" t="n">
-        <v>7037884</v>
+        <v>7038375</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5298,6 +5298,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-01-25</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>färska hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5324,10 +5329,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122360804</v>
+        <v>122360810</v>
       </c>
       <c r="B43" t="n">
-        <v>57374</v>
+        <v>90797</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5340,21 +5345,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5364,10 +5369,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>442349</v>
+        <v>442871</v>
       </c>
       <c r="R43" t="n">
-        <v>7037933</v>
+        <v>7038224</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5400,11 +5405,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-01-25</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5533,7 +5533,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122360803</v>
+        <v>122360804</v>
       </c>
       <c r="B45" t="n">
         <v>57374</v>
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>442741</v>
+        <v>442349</v>
       </c>
       <c r="R45" t="n">
-        <v>7038374</v>
+        <v>7037933</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5640,7 +5640,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122360811</v>
+        <v>122360808</v>
       </c>
       <c r="B46" t="n">
         <v>90797</v>
@@ -5680,10 +5680,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>442796</v>
+        <v>442718</v>
       </c>
       <c r="R46" t="n">
-        <v>7038234</v>
+        <v>7038356</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5742,7 +5742,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122360808</v>
+        <v>122360816</v>
       </c>
       <c r="B47" t="n">
         <v>90797</v>
@@ -5782,10 +5782,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>442718</v>
+        <v>442316</v>
       </c>
       <c r="R47" t="n">
-        <v>7038356</v>
+        <v>7037889</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5844,7 +5844,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122360809</v>
+        <v>122360812</v>
       </c>
       <c r="B48" t="n">
         <v>90797</v>
@@ -5884,10 +5884,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>442775</v>
+        <v>442794</v>
       </c>
       <c r="R48" t="n">
-        <v>7038300</v>
+        <v>7038245</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5946,10 +5946,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122360807</v>
+        <v>122360809</v>
       </c>
       <c r="B49" t="n">
-        <v>57485</v>
+        <v>90797</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5958,50 +5958,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103031</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Orrflon, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>442372</v>
+        <v>442775</v>
       </c>
       <c r="R49" t="n">
-        <v>7037810</v>
+        <v>7038300</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6060,10 +6048,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122360812</v>
+        <v>122360807</v>
       </c>
       <c r="B50" t="n">
-        <v>90797</v>
+        <v>57485</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6072,38 +6060,50 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Orrflon, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>442794</v>
+        <v>442372</v>
       </c>
       <c r="R50" t="n">
-        <v>7038245</v>
+        <v>7037810</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6162,7 +6162,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122360816</v>
+        <v>122360811</v>
       </c>
       <c r="B51" t="n">
         <v>90797</v>
@@ -6202,10 +6202,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>442316</v>
+        <v>442796</v>
       </c>
       <c r="R51" t="n">
-        <v>7037889</v>
+        <v>7038234</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>

--- a/artfynd/A 57103-2024 artfynd.xlsx
+++ b/artfynd/A 57103-2024 artfynd.xlsx
@@ -6264,10 +6264,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122488932</v>
+        <v>122488940</v>
       </c>
       <c r="B52" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442398</v>
+        <v>442302</v>
       </c>
       <c r="R52" t="n">
-        <v>7038117</v>
+        <v>7037892</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122488936</v>
+        <v>122488926</v>
       </c>
       <c r="B53" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442490</v>
+        <v>442896</v>
       </c>
       <c r="R53" t="n">
-        <v>7037858</v>
+        <v>7038243</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6468,10 +6468,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122488910</v>
+        <v>122488928</v>
       </c>
       <c r="B54" t="n">
-        <v>90905</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6480,25 +6480,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6508,10 +6508,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442798</v>
+        <v>442854</v>
       </c>
       <c r="R54" t="n">
-        <v>7038151</v>
+        <v>7038217</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122488920</v>
+        <v>122488917</v>
       </c>
       <c r="B55" t="n">
-        <v>78762</v>
+        <v>90962</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6586,21 +6586,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>442701</v>
+        <v>442706</v>
       </c>
       <c r="R55" t="n">
-        <v>7038299</v>
+        <v>7038136</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6672,10 +6672,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122488911</v>
+        <v>122488931</v>
       </c>
       <c r="B56" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6688,21 +6688,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6712,10 +6712,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>442336</v>
+        <v>442580</v>
       </c>
       <c r="R56" t="n">
-        <v>7037856</v>
+        <v>7038071</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6774,10 +6774,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122488918</v>
+        <v>122488911</v>
       </c>
       <c r="B57" t="n">
-        <v>90958</v>
+        <v>90944</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6790,21 +6790,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442290</v>
+        <v>442336</v>
       </c>
       <c r="R57" t="n">
-        <v>7038054</v>
+        <v>7037856</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6876,10 +6876,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122488913</v>
+        <v>122488925</v>
       </c>
       <c r="B58" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6892,21 +6892,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442578</v>
+        <v>442874</v>
       </c>
       <c r="R58" t="n">
-        <v>7038145</v>
+        <v>7038289</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6978,10 +6978,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122488941</v>
+        <v>122488913</v>
       </c>
       <c r="B59" t="n">
-        <v>78762</v>
+        <v>90962</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6994,21 +6994,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442229</v>
+        <v>442578</v>
       </c>
       <c r="R59" t="n">
-        <v>7037864</v>
+        <v>7038145</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7080,10 +7080,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122488938</v>
+        <v>122488929</v>
       </c>
       <c r="B60" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442367</v>
+        <v>442855</v>
       </c>
       <c r="R60" t="n">
-        <v>7037798</v>
+        <v>7038136</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7182,10 +7182,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122488928</v>
+        <v>122488921</v>
       </c>
       <c r="B61" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7222,10 +7222,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442854</v>
+        <v>442723</v>
       </c>
       <c r="R61" t="n">
-        <v>7038217</v>
+        <v>7038284</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7284,10 +7284,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122488917</v>
+        <v>122488939</v>
       </c>
       <c r="B62" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7300,21 +7300,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7324,10 +7324,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442706</v>
+        <v>442336</v>
       </c>
       <c r="R62" t="n">
-        <v>7038136</v>
+        <v>7037856</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7386,10 +7386,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122488937</v>
+        <v>122488919</v>
       </c>
       <c r="B63" t="n">
-        <v>78762</v>
+        <v>90962</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7402,21 +7402,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7426,10 +7426,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442405</v>
+        <v>442336</v>
       </c>
       <c r="R63" t="n">
-        <v>7037826</v>
+        <v>7037856</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7488,7 +7488,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122488907</v>
+        <v>122488908</v>
       </c>
       <c r="B64" t="n">
         <v>74863</v>
@@ -7528,10 +7528,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>442896</v>
+        <v>442856</v>
       </c>
       <c r="R64" t="n">
-        <v>7038243</v>
+        <v>7038154</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7590,10 +7590,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122488921</v>
+        <v>122488930</v>
       </c>
       <c r="B65" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7630,10 +7630,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>442723</v>
+        <v>442791</v>
       </c>
       <c r="R65" t="n">
-        <v>7038284</v>
+        <v>7038137</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7692,10 +7692,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122488933</v>
+        <v>122488936</v>
       </c>
       <c r="B66" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>442252</v>
+        <v>442490</v>
       </c>
       <c r="R66" t="n">
-        <v>7038020</v>
+        <v>7037858</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7794,10 +7794,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122488906</v>
+        <v>122488933</v>
       </c>
       <c r="B67" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7810,21 +7810,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7834,10 +7834,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>442878</v>
+        <v>442252</v>
       </c>
       <c r="R67" t="n">
-        <v>7038293</v>
+        <v>7038020</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7896,10 +7896,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122488926</v>
+        <v>122488909</v>
       </c>
       <c r="B68" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7912,21 +7912,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>442896</v>
+        <v>442556</v>
       </c>
       <c r="R68" t="n">
-        <v>7038243</v>
+        <v>7038106</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7980,6 +7980,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7998,10 +7999,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122488940</v>
+        <v>122488941</v>
       </c>
       <c r="B69" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8038,10 +8039,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>442302</v>
+        <v>442229</v>
       </c>
       <c r="R69" t="n">
-        <v>7037892</v>
+        <v>7037864</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -8100,10 +8101,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122488919</v>
+        <v>122488918</v>
       </c>
       <c r="B70" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8140,10 +8141,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>442336</v>
+        <v>442290</v>
       </c>
       <c r="R70" t="n">
-        <v>7037856</v>
+        <v>7038054</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8202,10 +8203,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122488935</v>
+        <v>122488937</v>
       </c>
       <c r="B71" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8242,10 +8243,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>442416</v>
+        <v>442405</v>
       </c>
       <c r="R71" t="n">
-        <v>7037865</v>
+        <v>7037826</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8304,10 +8305,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122488908</v>
+        <v>122488934</v>
       </c>
       <c r="B72" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8320,21 +8321,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8344,10 +8345,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>442856</v>
+        <v>442317</v>
       </c>
       <c r="R72" t="n">
-        <v>7038154</v>
+        <v>7037892</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8406,10 +8407,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122488929</v>
+        <v>122488906</v>
       </c>
       <c r="B73" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8422,21 +8423,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8446,10 +8447,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>442855</v>
+        <v>442878</v>
       </c>
       <c r="R73" t="n">
-        <v>7038136</v>
+        <v>7038293</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8508,10 +8509,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122488914</v>
+        <v>122488920</v>
       </c>
       <c r="B74" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8524,21 +8525,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8610,10 +8611,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122488930</v>
+        <v>122488907</v>
       </c>
       <c r="B75" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8626,21 +8627,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8650,10 +8651,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>442791</v>
+        <v>442896</v>
       </c>
       <c r="R75" t="n">
-        <v>7038137</v>
+        <v>7038243</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8712,10 +8713,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122488931</v>
+        <v>122488938</v>
       </c>
       <c r="B76" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8752,10 +8753,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>442580</v>
+        <v>442367</v>
       </c>
       <c r="R76" t="n">
-        <v>7038071</v>
+        <v>7037798</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8817,7 +8818,7 @@
         <v>122488916</v>
       </c>
       <c r="B77" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8916,10 +8917,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122488925</v>
+        <v>122488935</v>
       </c>
       <c r="B78" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8956,10 +8957,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>442874</v>
+        <v>442416</v>
       </c>
       <c r="R78" t="n">
-        <v>7038289</v>
+        <v>7037865</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -9018,10 +9019,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122488939</v>
+        <v>122488932</v>
       </c>
       <c r="B79" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9058,10 +9059,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>442336</v>
+        <v>442398</v>
       </c>
       <c r="R79" t="n">
-        <v>7037856</v>
+        <v>7038117</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9120,10 +9121,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122488934</v>
+        <v>122488910</v>
       </c>
       <c r="B80" t="n">
-        <v>78762</v>
+        <v>90909</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9132,25 +9133,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9160,10 +9161,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>442317</v>
+        <v>442798</v>
       </c>
       <c r="R80" t="n">
-        <v>7037892</v>
+        <v>7038151</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -9222,10 +9223,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122488909</v>
+        <v>122488914</v>
       </c>
       <c r="B81" t="n">
-        <v>74863</v>
+        <v>90962</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9238,21 +9239,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9262,10 +9263,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>442556</v>
+        <v>442701</v>
       </c>
       <c r="R81" t="n">
-        <v>7038106</v>
+        <v>7038299</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>
@@ -9306,7 +9307,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57103-2024 artfynd.xlsx
+++ b/artfynd/A 57103-2024 artfynd.xlsx
@@ -6264,7 +6264,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122488940</v>
+        <v>122488920</v>
       </c>
       <c r="B52" t="n">
         <v>78766</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442302</v>
+        <v>442701</v>
       </c>
       <c r="R52" t="n">
-        <v>7037892</v>
+        <v>7038299</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6366,7 +6366,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122488926</v>
+        <v>122488941</v>
       </c>
       <c r="B53" t="n">
         <v>78766</v>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442896</v>
+        <v>442229</v>
       </c>
       <c r="R53" t="n">
-        <v>7038243</v>
+        <v>7037864</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122488928</v>
+        <v>122488938</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6508,10 +6508,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442854</v>
+        <v>442367</v>
       </c>
       <c r="R54" t="n">
-        <v>7038217</v>
+        <v>7037798</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6570,7 +6570,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122488917</v>
+        <v>122488913</v>
       </c>
       <c r="B55" t="n">
         <v>90962</v>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>442706</v>
+        <v>442578</v>
       </c>
       <c r="R55" t="n">
-        <v>7038136</v>
+        <v>7038145</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -6672,7 +6672,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122488931</v>
+        <v>122488921</v>
       </c>
       <c r="B56" t="n">
         <v>78766</v>
@@ -6712,10 +6712,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>442580</v>
+        <v>442723</v>
       </c>
       <c r="R56" t="n">
-        <v>7038071</v>
+        <v>7038284</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6774,10 +6774,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122488911</v>
+        <v>122488919</v>
       </c>
       <c r="B57" t="n">
-        <v>90944</v>
+        <v>90962</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6790,21 +6790,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6876,10 +6876,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122488925</v>
+        <v>122488911</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6892,21 +6892,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442874</v>
+        <v>442336</v>
       </c>
       <c r="R58" t="n">
-        <v>7038289</v>
+        <v>7037856</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6978,7 +6978,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122488913</v>
+        <v>122488916</v>
       </c>
       <c r="B59" t="n">
         <v>90962</v>
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442578</v>
+        <v>442776</v>
       </c>
       <c r="R59" t="n">
-        <v>7038145</v>
+        <v>7038303</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7080,7 +7080,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122488929</v>
+        <v>122488936</v>
       </c>
       <c r="B60" t="n">
         <v>78766</v>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442855</v>
+        <v>442490</v>
       </c>
       <c r="R60" t="n">
-        <v>7038136</v>
+        <v>7037858</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7182,7 +7182,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122488921</v>
+        <v>122488931</v>
       </c>
       <c r="B61" t="n">
         <v>78766</v>
@@ -7222,10 +7222,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442723</v>
+        <v>442580</v>
       </c>
       <c r="R61" t="n">
-        <v>7038284</v>
+        <v>7038071</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7284,10 +7284,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122488939</v>
+        <v>122488906</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7300,21 +7300,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7324,10 +7324,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442336</v>
+        <v>442878</v>
       </c>
       <c r="R62" t="n">
-        <v>7037856</v>
+        <v>7038293</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7386,7 +7386,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122488919</v>
+        <v>122488917</v>
       </c>
       <c r="B63" t="n">
         <v>90962</v>
@@ -7426,10 +7426,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442336</v>
+        <v>442706</v>
       </c>
       <c r="R63" t="n">
-        <v>7037856</v>
+        <v>7038136</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7488,10 +7488,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122488908</v>
+        <v>122488940</v>
       </c>
       <c r="B64" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7504,21 +7504,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7528,10 +7528,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>442856</v>
+        <v>442302</v>
       </c>
       <c r="R64" t="n">
-        <v>7038154</v>
+        <v>7037892</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7590,10 +7590,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122488930</v>
+        <v>122488907</v>
       </c>
       <c r="B65" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7606,21 +7606,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7630,10 +7630,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>442791</v>
+        <v>442896</v>
       </c>
       <c r="R65" t="n">
-        <v>7038137</v>
+        <v>7038243</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7692,7 +7692,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122488936</v>
+        <v>122488928</v>
       </c>
       <c r="B66" t="n">
         <v>78766</v>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>442490</v>
+        <v>442854</v>
       </c>
       <c r="R66" t="n">
-        <v>7037858</v>
+        <v>7038217</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122488933</v>
+        <v>122488930</v>
       </c>
       <c r="B67" t="n">
         <v>78766</v>
@@ -7834,10 +7834,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>442252</v>
+        <v>442791</v>
       </c>
       <c r="R67" t="n">
-        <v>7038020</v>
+        <v>7038137</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7896,10 +7896,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122488909</v>
+        <v>122488910</v>
       </c>
       <c r="B68" t="n">
-        <v>74863</v>
+        <v>90909</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7908,25 +7908,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>442556</v>
+        <v>442798</v>
       </c>
       <c r="R68" t="n">
-        <v>7038106</v>
+        <v>7038151</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7980,7 +7980,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7999,7 +7998,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122488941</v>
+        <v>122488933</v>
       </c>
       <c r="B69" t="n">
         <v>78766</v>
@@ -8039,10 +8038,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>442229</v>
+        <v>442252</v>
       </c>
       <c r="R69" t="n">
-        <v>7037864</v>
+        <v>7038020</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -8101,10 +8100,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122488918</v>
+        <v>122488908</v>
       </c>
       <c r="B70" t="n">
-        <v>90962</v>
+        <v>74863</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8117,21 +8116,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8141,10 +8140,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>442290</v>
+        <v>442856</v>
       </c>
       <c r="R70" t="n">
-        <v>7038054</v>
+        <v>7038154</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8203,7 +8202,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122488937</v>
+        <v>122488926</v>
       </c>
       <c r="B71" t="n">
         <v>78766</v>
@@ -8243,10 +8242,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>442405</v>
+        <v>442896</v>
       </c>
       <c r="R71" t="n">
-        <v>7037826</v>
+        <v>7038243</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8305,10 +8304,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122488934</v>
+        <v>122488914</v>
       </c>
       <c r="B72" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8321,21 +8320,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8345,10 +8344,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>442317</v>
+        <v>442701</v>
       </c>
       <c r="R72" t="n">
-        <v>7037892</v>
+        <v>7038299</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8407,10 +8406,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122488906</v>
+        <v>122488918</v>
       </c>
       <c r="B73" t="n">
-        <v>74863</v>
+        <v>90962</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8423,21 +8422,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8447,10 +8446,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>442878</v>
+        <v>442290</v>
       </c>
       <c r="R73" t="n">
-        <v>7038293</v>
+        <v>7038054</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8509,10 +8508,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122488920</v>
+        <v>122488909</v>
       </c>
       <c r="B74" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8525,21 +8524,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8549,10 +8548,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>442701</v>
+        <v>442556</v>
       </c>
       <c r="R74" t="n">
-        <v>7038299</v>
+        <v>7038106</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8593,6 +8592,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8611,10 +8611,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122488907</v>
+        <v>122488937</v>
       </c>
       <c r="B75" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8627,21 +8627,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8651,10 +8651,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>442896</v>
+        <v>442405</v>
       </c>
       <c r="R75" t="n">
-        <v>7038243</v>
+        <v>7037826</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8713,7 +8713,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122488938</v>
+        <v>122488935</v>
       </c>
       <c r="B76" t="n">
         <v>78766</v>
@@ -8753,10 +8753,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>442367</v>
+        <v>442416</v>
       </c>
       <c r="R76" t="n">
-        <v>7037798</v>
+        <v>7037865</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8815,10 +8815,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122488916</v>
+        <v>122488932</v>
       </c>
       <c r="B77" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8831,21 +8831,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>442776</v>
+        <v>442398</v>
       </c>
       <c r="R77" t="n">
-        <v>7038303</v>
+        <v>7038117</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8917,7 +8917,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122488935</v>
+        <v>122488939</v>
       </c>
       <c r="B78" t="n">
         <v>78766</v>
@@ -8957,10 +8957,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>442416</v>
+        <v>442336</v>
       </c>
       <c r="R78" t="n">
-        <v>7037865</v>
+        <v>7037856</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -9019,7 +9019,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122488932</v>
+        <v>122488925</v>
       </c>
       <c r="B79" t="n">
         <v>78766</v>
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>442398</v>
+        <v>442874</v>
       </c>
       <c r="R79" t="n">
-        <v>7038117</v>
+        <v>7038289</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9121,10 +9121,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122488910</v>
+        <v>122488929</v>
       </c>
       <c r="B80" t="n">
-        <v>90909</v>
+        <v>78766</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9133,25 +9133,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9161,10 +9161,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>442798</v>
+        <v>442855</v>
       </c>
       <c r="R80" t="n">
-        <v>7038151</v>
+        <v>7038136</v>
       </c>
       <c r="S80" t="n">
         <v>20</v>
@@ -9223,10 +9223,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122488914</v>
+        <v>122488934</v>
       </c>
       <c r="B81" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9239,21 +9239,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9263,10 +9263,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>442701</v>
+        <v>442317</v>
       </c>
       <c r="R81" t="n">
-        <v>7038299</v>
+        <v>7037892</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>

--- a/artfynd/A 57103-2024 artfynd.xlsx
+++ b/artfynd/A 57103-2024 artfynd.xlsx
@@ -6264,7 +6264,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122488920</v>
+        <v>122488921</v>
       </c>
       <c r="B52" t="n">
         <v>78766</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442701</v>
+        <v>442723</v>
       </c>
       <c r="R52" t="n">
-        <v>7038299</v>
+        <v>7038284</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122488941</v>
+        <v>122488908</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6382,21 +6382,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442229</v>
+        <v>442856</v>
       </c>
       <c r="R53" t="n">
-        <v>7037864</v>
+        <v>7038154</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6468,7 +6468,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122488938</v>
+        <v>122488931</v>
       </c>
       <c r="B54" t="n">
         <v>78766</v>
@@ -6508,10 +6508,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442367</v>
+        <v>442580</v>
       </c>
       <c r="R54" t="n">
-        <v>7037798</v>
+        <v>7038071</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6672,7 +6672,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122488921</v>
+        <v>122488933</v>
       </c>
       <c r="B56" t="n">
         <v>78766</v>
@@ -6712,10 +6712,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>442723</v>
+        <v>442252</v>
       </c>
       <c r="R56" t="n">
-        <v>7038284</v>
+        <v>7038020</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6774,10 +6774,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122488919</v>
+        <v>122488906</v>
       </c>
       <c r="B57" t="n">
-        <v>90962</v>
+        <v>74863</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6790,21 +6790,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>442336</v>
+        <v>442878</v>
       </c>
       <c r="R57" t="n">
-        <v>7037856</v>
+        <v>7038293</v>
       </c>
       <c r="S57" t="n">
         <v>20</v>
@@ -6876,10 +6876,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122488911</v>
+        <v>122488907</v>
       </c>
       <c r="B58" t="n">
-        <v>90944</v>
+        <v>74863</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6892,21 +6892,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6916,10 +6916,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>442336</v>
+        <v>442896</v>
       </c>
       <c r="R58" t="n">
-        <v>7037856</v>
+        <v>7038243</v>
       </c>
       <c r="S58" t="n">
         <v>20</v>
@@ -6978,10 +6978,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122488916</v>
+        <v>122488925</v>
       </c>
       <c r="B59" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6994,21 +6994,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7018,10 +7018,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>442776</v>
+        <v>442874</v>
       </c>
       <c r="R59" t="n">
-        <v>7038303</v>
+        <v>7038289</v>
       </c>
       <c r="S59" t="n">
         <v>20</v>
@@ -7080,7 +7080,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122488936</v>
+        <v>122488926</v>
       </c>
       <c r="B60" t="n">
         <v>78766</v>
@@ -7120,10 +7120,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>442490</v>
+        <v>442896</v>
       </c>
       <c r="R60" t="n">
-        <v>7037858</v>
+        <v>7038243</v>
       </c>
       <c r="S60" t="n">
         <v>20</v>
@@ -7182,7 +7182,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122488931</v>
+        <v>122488928</v>
       </c>
       <c r="B61" t="n">
         <v>78766</v>
@@ -7222,10 +7222,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>442580</v>
+        <v>442854</v>
       </c>
       <c r="R61" t="n">
-        <v>7038071</v>
+        <v>7038217</v>
       </c>
       <c r="S61" t="n">
         <v>20</v>
@@ -7284,10 +7284,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122488906</v>
+        <v>122488917</v>
       </c>
       <c r="B62" t="n">
-        <v>74863</v>
+        <v>90962</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7300,21 +7300,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7324,10 +7324,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>442878</v>
+        <v>442706</v>
       </c>
       <c r="R62" t="n">
-        <v>7038293</v>
+        <v>7038136</v>
       </c>
       <c r="S62" t="n">
         <v>20</v>
@@ -7386,7 +7386,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122488917</v>
+        <v>122488919</v>
       </c>
       <c r="B63" t="n">
         <v>90962</v>
@@ -7426,10 +7426,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442706</v>
+        <v>442336</v>
       </c>
       <c r="R63" t="n">
-        <v>7038136</v>
+        <v>7037856</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7488,7 +7488,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122488940</v>
+        <v>122488920</v>
       </c>
       <c r="B64" t="n">
         <v>78766</v>
@@ -7528,10 +7528,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>442302</v>
+        <v>442701</v>
       </c>
       <c r="R64" t="n">
-        <v>7037892</v>
+        <v>7038299</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7590,10 +7590,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122488907</v>
+        <v>122488916</v>
       </c>
       <c r="B65" t="n">
-        <v>74863</v>
+        <v>90962</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7606,21 +7606,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7630,10 +7630,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>442896</v>
+        <v>442776</v>
       </c>
       <c r="R65" t="n">
-        <v>7038243</v>
+        <v>7038303</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7692,10 +7692,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122488928</v>
+        <v>122488918</v>
       </c>
       <c r="B66" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7708,21 +7708,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>442854</v>
+        <v>442290</v>
       </c>
       <c r="R66" t="n">
-        <v>7038217</v>
+        <v>7038054</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122488930</v>
+        <v>122488940</v>
       </c>
       <c r="B67" t="n">
         <v>78766</v>
@@ -7834,10 +7834,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>442791</v>
+        <v>442302</v>
       </c>
       <c r="R67" t="n">
-        <v>7038137</v>
+        <v>7037892</v>
       </c>
       <c r="S67" t="n">
         <v>20</v>
@@ -7896,10 +7896,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122488910</v>
+        <v>122488939</v>
       </c>
       <c r="B68" t="n">
-        <v>90909</v>
+        <v>78766</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7908,25 +7908,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>442798</v>
+        <v>442336</v>
       </c>
       <c r="R68" t="n">
-        <v>7038151</v>
+        <v>7037856</v>
       </c>
       <c r="S68" t="n">
         <v>20</v>
@@ -7998,10 +7998,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122488933</v>
+        <v>122488910</v>
       </c>
       <c r="B69" t="n">
-        <v>78766</v>
+        <v>90909</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8010,25 +8010,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>442252</v>
+        <v>442798</v>
       </c>
       <c r="R69" t="n">
-        <v>7038020</v>
+        <v>7038151</v>
       </c>
       <c r="S69" t="n">
         <v>20</v>
@@ -8100,10 +8100,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122488908</v>
+        <v>122488932</v>
       </c>
       <c r="B70" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8116,21 +8116,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8140,10 +8140,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>442856</v>
+        <v>442398</v>
       </c>
       <c r="R70" t="n">
-        <v>7038154</v>
+        <v>7038117</v>
       </c>
       <c r="S70" t="n">
         <v>20</v>
@@ -8202,7 +8202,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122488926</v>
+        <v>122488937</v>
       </c>
       <c r="B71" t="n">
         <v>78766</v>
@@ -8242,10 +8242,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>442896</v>
+        <v>442405</v>
       </c>
       <c r="R71" t="n">
-        <v>7038243</v>
+        <v>7037826</v>
       </c>
       <c r="S71" t="n">
         <v>20</v>
@@ -8304,10 +8304,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122488914</v>
+        <v>122488941</v>
       </c>
       <c r="B72" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8320,21 +8320,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8344,10 +8344,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>442701</v>
+        <v>442229</v>
       </c>
       <c r="R72" t="n">
-        <v>7038299</v>
+        <v>7037864</v>
       </c>
       <c r="S72" t="n">
         <v>20</v>
@@ -8406,10 +8406,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122488918</v>
+        <v>122488935</v>
       </c>
       <c r="B73" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8422,21 +8422,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8446,10 +8446,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>442290</v>
+        <v>442416</v>
       </c>
       <c r="R73" t="n">
-        <v>7038054</v>
+        <v>7037865</v>
       </c>
       <c r="S73" t="n">
         <v>20</v>
@@ -8508,10 +8508,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122488909</v>
+        <v>122488938</v>
       </c>
       <c r="B74" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8524,21 +8524,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8548,10 +8548,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>442556</v>
+        <v>442367</v>
       </c>
       <c r="R74" t="n">
-        <v>7038106</v>
+        <v>7037798</v>
       </c>
       <c r="S74" t="n">
         <v>20</v>
@@ -8592,7 +8592,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8611,7 +8610,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122488937</v>
+        <v>122488936</v>
       </c>
       <c r="B75" t="n">
         <v>78766</v>
@@ -8651,10 +8650,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>442405</v>
+        <v>442490</v>
       </c>
       <c r="R75" t="n">
-        <v>7037826</v>
+        <v>7037858</v>
       </c>
       <c r="S75" t="n">
         <v>20</v>
@@ -8713,10 +8712,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122488935</v>
+        <v>122488914</v>
       </c>
       <c r="B76" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8729,21 +8728,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8753,10 +8752,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>442416</v>
+        <v>442701</v>
       </c>
       <c r="R76" t="n">
-        <v>7037865</v>
+        <v>7038299</v>
       </c>
       <c r="S76" t="n">
         <v>20</v>
@@ -8815,10 +8814,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122488932</v>
+        <v>122488909</v>
       </c>
       <c r="B77" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8831,21 +8830,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8855,10 +8854,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>442398</v>
+        <v>442556</v>
       </c>
       <c r="R77" t="n">
-        <v>7038117</v>
+        <v>7038106</v>
       </c>
       <c r="S77" t="n">
         <v>20</v>
@@ -8899,6 +8898,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8917,7 +8917,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122488939</v>
+        <v>122488934</v>
       </c>
       <c r="B78" t="n">
         <v>78766</v>
@@ -8957,10 +8957,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>442336</v>
+        <v>442317</v>
       </c>
       <c r="R78" t="n">
-        <v>7037856</v>
+        <v>7037892</v>
       </c>
       <c r="S78" t="n">
         <v>20</v>
@@ -9019,10 +9019,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122488925</v>
+        <v>122488911</v>
       </c>
       <c r="B79" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9035,21 +9035,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9059,10 +9059,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>442874</v>
+        <v>442336</v>
       </c>
       <c r="R79" t="n">
-        <v>7038289</v>
+        <v>7037856</v>
       </c>
       <c r="S79" t="n">
         <v>20</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122488934</v>
+        <v>122488930</v>
       </c>
       <c r="B81" t="n">
         <v>78766</v>
@@ -9263,10 +9263,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>442317</v>
+        <v>442791</v>
       </c>
       <c r="R81" t="n">
-        <v>7037892</v>
+        <v>7038137</v>
       </c>
       <c r="S81" t="n">
         <v>20</v>

--- a/artfynd/A 57103-2024 artfynd.xlsx
+++ b/artfynd/A 57103-2024 artfynd.xlsx
@@ -6264,10 +6264,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122488921</v>
+        <v>122488913</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6280,21 +6280,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>442723</v>
+        <v>442578</v>
       </c>
       <c r="R52" t="n">
-        <v>7038284</v>
+        <v>7038145</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6366,10 +6366,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122488908</v>
+        <v>122488921</v>
       </c>
       <c r="B53" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6382,21 +6382,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6406,10 +6406,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>442856</v>
+        <v>442723</v>
       </c>
       <c r="R53" t="n">
-        <v>7038154</v>
+        <v>7038284</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6468,10 +6468,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122488931</v>
+        <v>122488908</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6484,21 +6484,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6508,10 +6508,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>442580</v>
+        <v>442856</v>
       </c>
       <c r="R54" t="n">
-        <v>7038071</v>
+        <v>7038154</v>
       </c>
       <c r="S54" t="n">
         <v>20</v>
@@ -6570,10 +6570,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122488913</v>
+        <v>122488931</v>
       </c>
       <c r="B55" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6586,21 +6586,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>442578</v>
+        <v>442580</v>
       </c>
       <c r="R55" t="n">
-        <v>7038145</v>
+        <v>7038071</v>
       </c>
       <c r="S55" t="n">
         <v>20</v>
@@ -7386,7 +7386,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122488919</v>
+        <v>122488916</v>
       </c>
       <c r="B63" t="n">
         <v>90962</v>
@@ -7426,10 +7426,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>442336</v>
+        <v>442776</v>
       </c>
       <c r="R63" t="n">
-        <v>7037856</v>
+        <v>7038303</v>
       </c>
       <c r="S63" t="n">
         <v>20</v>
@@ -7488,10 +7488,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122488920</v>
+        <v>122488918</v>
       </c>
       <c r="B64" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7504,21 +7504,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7528,10 +7528,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>442701</v>
+        <v>442290</v>
       </c>
       <c r="R64" t="n">
-        <v>7038299</v>
+        <v>7038054</v>
       </c>
       <c r="S64" t="n">
         <v>20</v>
@@ -7590,7 +7590,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122488916</v>
+        <v>122488919</v>
       </c>
       <c r="B65" t="n">
         <v>90962</v>
@@ -7630,10 +7630,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>442776</v>
+        <v>442336</v>
       </c>
       <c r="R65" t="n">
-        <v>7038303</v>
+        <v>7037856</v>
       </c>
       <c r="S65" t="n">
         <v>20</v>
@@ -7692,10 +7692,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122488918</v>
+        <v>122488920</v>
       </c>
       <c r="B66" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7708,21 +7708,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7732,10 +7732,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>442290</v>
+        <v>442701</v>
       </c>
       <c r="R66" t="n">
-        <v>7038054</v>
+        <v>7038299</v>
       </c>
       <c r="S66" t="n">
         <v>20</v>
